--- a/List_Info_User.xlsx
+++ b/List_Info_User.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI168"/>
+  <dimension ref="A1:AK168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -604,6 +604,16 @@
           <t>Hành Động Đội Sales (Sales Action)</t>
         </is>
       </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Country / Quốc Gia</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Country / Quốc Gia</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -705,15 +715,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>https://amzn.to/2Qi8QNt</t>
@@ -735,6 +736,16 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -904,6 +915,16 @@
           <t>Gọi điện thoại trực tiếp hỏi: 'Do you provide a puppy take-home package?' + Gửi báo giá sỉ V2 Standard Kit</t>
         </is>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -954,7 +975,6 @@
           <t>https://www.instagram.com/curlytaildoodles/</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">harrisonburg </t>
@@ -962,7 +982,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1001,16 +1021,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -1027,6 +1037,16 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -1130,16 +1150,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -1156,6 +1166,16 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1322,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -1319,6 +1338,16 @@
       <c r="AI6" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -1422,16 +1451,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -1448,6 +1467,16 @@
       <c r="AI7" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1544,6 @@
           <t>OR</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>United States</t>
@@ -1547,16 +1575,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -1573,6 +1591,16 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1747,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -1736,6 +1763,16 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -1839,15 +1876,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>https://www.amazon.com/shop/mama.bryner</t>
@@ -1869,6 +1897,16 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1959,6 @@
           <t>https://www.instagram.com/golden_ticket_puppies/</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>United States</t>
@@ -1956,16 +1990,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -1982,6 +2006,16 @@
       <c r="AI11" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2162,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -2145,6 +2178,16 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2255,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>United States</t>
@@ -2244,15 +2286,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>https://amzn.to/2oKsBMG</t>
@@ -2274,6 +2307,16 @@
       <c r="AI13" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -2377,16 +2420,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -2403,6 +2436,16 @@
       <c r="AI14" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -2455,7 +2498,6 @@
           <t>https://www.instagram.com/paula_pacificcrestlabradors/</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>Ranchita</t>
@@ -2502,16 +2544,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -2528,6 +2560,16 @@
       <c r="AI15" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -2570,13 +2612,11 @@
           <t>https://www.facebook.com/windsongdoodles/</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>https://www.instagram.com/windsongdoodles/</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>Southern California</t>
@@ -2587,7 +2627,6 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>United States</t>
@@ -2619,16 +2658,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -2645,6 +2674,16 @@
       <c r="AI16" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2736,6 @@
           <t>https://www.instagram.com/new2urescue585/</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>United States</t>
@@ -2732,16 +2767,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -2758,6 +2783,16 @@
       <c r="AI17" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -2800,16 +2835,11 @@
           <t>https://www.facebook.com/SweetPinePuppies/</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>https://www.instagram.com/sweetpine_puppies/</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>United States</t>
@@ -2841,15 +2871,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>https://amzn.to/4aoRja1</t>
@@ -2871,6 +2892,16 @@
       <c r="AI18" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2954,6 @@
           <t>https://www.instagram.com/monsterbullykennel/; https://www.instagram.com/monsterbullykennels2/</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>PORTLAND</t>
@@ -2934,7 +2964,6 @@
           <t>OR</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>United States</t>
@@ -3009,7 +3038,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -3026,6 +3054,16 @@
       <c r="AI19" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3106,6 @@
           <t>https://www.facebook.com/BernedoodleForSale/</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>https://www.instagram.com/shadyoakdoodles/</t>
@@ -3168,7 +3205,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -3185,6 +3221,16 @@
       <c r="AI20" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -3288,16 +3334,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -3314,6 +3350,16 @@
       <c r="AI21" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3506,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -3477,6 +3522,16 @@
       <c r="AI22" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3584,6 @@
           <t>https://www.instagram.com/salemsfinestakcchihuahuas/</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>Salem</t>
@@ -3576,15 +3630,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr">
         <is>
           <t>https://www.amazon.com/shop/salemsfinestakcchihuahuas?ref_=cm_sw_r_cp_ud_aipsfshop_27VCW6HAZRN4NPC95V4S</t>
@@ -3606,6 +3651,16 @@
       <c r="AI23" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -3709,16 +3764,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -3735,6 +3780,16 @@
       <c r="AI24" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -3838,16 +3893,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -3864,6 +3909,16 @@
       <c r="AI25" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -3967,16 +4022,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -3993,6 +4038,16 @@
       <c r="AI26" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -4045,10 +4100,6 @@
           <t>https://www.instagram.com/rochesternydogs/</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>Rochester</t>
@@ -4080,16 +4131,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -4106,6 +4147,16 @@
       <c r="AI27" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4209,6 @@
           <t>https://www.instagram.com/cashmerecavapoosca/</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>​​San Diego</t>
@@ -4169,7 +4219,6 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>San Diego</t>
@@ -4244,7 +4293,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -4261,6 +4309,16 @@
       <c r="AI28" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4386,6 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>California</t>
@@ -4360,15 +4417,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr">
         <is>
           <t>https://www.amazon.com/shop/dreamgoldenretrievers</t>
@@ -4390,6 +4438,16 @@
       <c r="AI29" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -4432,16 +4490,11 @@
           <t>https://www.facebook.com/TeamReevesRanch/</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>https://www.instagram.com/teamreevesranch/</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>California</t>
@@ -4473,16 +4526,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -4499,6 +4542,16 @@
       <c r="AI30" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -4551,14 +4604,11 @@
           <t>https://www.instagram.com/red_white_and_doodle/</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>adoption-steps-desktop|1|0|0</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>US</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>United States</t>
@@ -4590,16 +4640,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -4616,6 +4656,16 @@
       <c r="AI31" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -4668,10 +4718,6 @@
           <t>https://www.instagram.com/motydomcattery/</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>United States</t>
@@ -4703,16 +4749,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -4729,6 +4765,16 @@
       <c r="AI32" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -4771,16 +4817,11 @@
           <t>https://www.facebook.com/SunsetRetrieverPuppies/</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>https://www.instagram.com/sunsetretrievers/</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>United States</t>
@@ -4812,16 +4853,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -4838,6 +4869,16 @@
       <c r="AI33" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -4941,16 +4982,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -4967,6 +4998,16 @@
       <c r="AI34" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -5070,16 +5111,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -5096,6 +5127,16 @@
       <c r="AI35" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -5143,8 +5184,6 @@
           <t>100067000000000</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>Rochester</t>
@@ -5155,7 +5194,6 @@
           <t>NY</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>Fairport United States</t>
@@ -5230,7 +5268,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -5247,6 +5284,16 @@
       <c r="AI36" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -5299,10 +5346,6 @@
           <t>https://www.instagram.com/bulkcampbullies/</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>North Dakota</t>
@@ -5334,16 +5377,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -5360,6 +5393,16 @@
       <c r="AI37" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5470,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>Virginia</t>
@@ -5459,16 +5501,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -5485,6 +5517,16 @@
       <c r="AI38" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -5527,7 +5569,6 @@
           <t>https://www.facebook.com/Bideawee/</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>https://www.instagram.com/bideawee/</t>
@@ -5627,7 +5668,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -5644,6 +5684,16 @@
       <c r="AI39" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -5686,8 +5736,6 @@
           <t>https://www.facebook.com/Central-Dakota-Humane-Society-344964339313/; https://www.facebook.com/centraldakotahumanesociety/</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>2104 37th Street</t>
@@ -5739,16 +5787,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
-      <c r="AB40" t="inlineStr"/>
-      <c r="AC40" t="inlineStr"/>
-      <c r="AD40" t="inlineStr"/>
-      <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -5765,6 +5803,16 @@
       <c r="AI40" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -5802,8 +5850,6 @@
           <t>https://www.goldenpuppies.com/</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>https://www.instagram.com/thegoldenbreeder/</t>
@@ -5860,15 +5906,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
-      <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="inlineStr">
         <is>
           <t>https://amzn.to/4cgcXiR</t>
@@ -5890,6 +5927,16 @@
       <c r="AI41" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -5932,20 +5979,16 @@
           <t>https://www.facebook.com/Posh-Puppies-109609068484039/</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>https://www.instagram.com/poshpuppies_official/</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>US</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
           <t>North Dakota</t>
@@ -5977,16 +6020,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
-      <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -6003,6 +6036,16 @@
       <c r="AI42" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -6045,16 +6088,11 @@
           <t>https://www.facebook.com/northwooddoodles/</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>https://www.instagram.com/northwooddoodles/</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>North Dakota</t>
@@ -6086,16 +6124,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr"/>
-      <c r="AC43" t="inlineStr"/>
-      <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -6112,6 +6140,16 @@
       <c r="AI43" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -6154,13 +6192,11 @@
           <t>https://www.facebook.com/Sierra-View-English-Creams-487391081611797/</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>https://www.instagram.com/sierraviewenglishcreamsretri/</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>Tollhouse</t>
@@ -6168,10 +6204,9 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>CA</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
           <t>California</t>
@@ -6203,16 +6238,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr"/>
-      <c r="AC44" t="inlineStr"/>
-      <c r="AD44" t="inlineStr"/>
-      <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -6229,6 +6254,16 @@
       <c r="AI44" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6311,6 @@
           <t>100065000000000</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>Chatham, Virginia, United States</t>
@@ -6328,16 +6362,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
-      <c r="AB45" t="inlineStr"/>
-      <c r="AC45" t="inlineStr"/>
-      <c r="AD45" t="inlineStr"/>
-      <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -6354,6 +6378,16 @@
       <c r="AI45" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6430,6 @@
           <t>https://www.facebook.com/NorthstarNewfoundlandMN/</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>https://www.instagram.com/northstarnewfoundlandsMN/</t>
@@ -6453,15 +6486,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
-      <c r="AB46" t="inlineStr"/>
-      <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="inlineStr">
         <is>
           <t>https://amzn.to/3X9JzEN</t>
@@ -6483,6 +6507,16 @@
       <c r="AI46" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -6525,7 +6559,6 @@
           <t>https://www.facebook.com/557710901234693/</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>https://www.instagram.com/mainecoonections/</t>
@@ -6625,7 +6658,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -6642,6 +6674,16 @@
       <c r="AI47" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6736,6 @@
           <t>https://www.instagram.com/ethicalfrenchie/</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>New York</t>
@@ -6702,7 +6743,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6784,7 +6825,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -6801,6 +6841,16 @@
       <c r="AI48" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -6843,13 +6893,11 @@
           <t>https://www.facebook.com/thecaninesociety/</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>https://www.instagram.com/the.canine.society/</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>Huntington Beach</t>
@@ -6860,7 +6908,6 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>California</t>
@@ -6892,16 +6939,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
-      <c r="AB49" t="inlineStr"/>
-      <c r="AC49" t="inlineStr"/>
-      <c r="AD49" t="inlineStr"/>
-      <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -6918,6 +6955,16 @@
       <c r="AI49" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -6955,8 +7002,6 @@
           <t>https://www.homewardonline.org/</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>https://www.instagram.com/homewardanimalshelter/</t>
@@ -7013,16 +7058,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr"/>
-      <c r="AC50" t="inlineStr"/>
-      <c r="AD50" t="inlineStr"/>
-      <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -7039,6 +7074,16 @@
       <c r="AI50" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7126,6 @@
           <t>https://www.facebook.com/tinycutiesnyc/</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>https://www.instagram.com/tiny_cuties_nyc/</t>
@@ -7138,16 +7182,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="inlineStr"/>
-      <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -7164,6 +7198,16 @@
       <c r="AI51" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -7201,8 +7245,6 @@
           <t>https://felius.org/</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>https://www.instagram.com/feliusomaha/</t>
@@ -7302,7 +7344,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -7319,6 +7360,16 @@
       <c r="AI52" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -7361,13 +7412,11 @@
           <t>https://www.facebook.com/CentralValleyGSD/</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>https://www.instagram.com/centralvalleygsd/</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>Central Valley</t>
@@ -7378,7 +7427,6 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>California</t>
@@ -7410,16 +7458,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
-      <c r="AB53" t="inlineStr"/>
-      <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr"/>
-      <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -7436,6 +7474,16 @@
       <c r="AI53" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7526,6 @@
           <t>https://www.facebook.com/Central.California.SPCA/</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>https://www.instagram.com/ccspca/</t>
@@ -7535,16 +7582,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
-      <c r="AC54" t="inlineStr"/>
-      <c r="AD54" t="inlineStr"/>
-      <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -7561,6 +7598,16 @@
       <c r="AI54" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -7603,16 +7650,11 @@
           <t>https://www.facebook.com/oregondogrescue/</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>https://www.instagram.com/oregondogrescue/</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>United States</t>
@@ -7644,16 +7686,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
-      <c r="AB55" t="inlineStr"/>
-      <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr"/>
-      <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -7670,6 +7702,16 @@
       <c r="AI55" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7764,6 @@
           <t>https://www.instagram.com/chateau_st._john_labradors/</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>Glendale</t>
@@ -7769,16 +7810,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
-      <c r="AB56" t="inlineStr"/>
-      <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="inlineStr"/>
-      <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -7795,6 +7826,16 @@
       <c r="AI56" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -7847,10 +7888,6 @@
           <t>https://www.instagram.com/AnimalKingdomPetGrooming/</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>United States</t>
@@ -7882,16 +7919,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
-      <c r="AB57" t="inlineStr"/>
-      <c r="AC57" t="inlineStr"/>
-      <c r="AD57" t="inlineStr"/>
-      <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -7908,6 +7935,16 @@
       <c r="AI57" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -8011,16 +8048,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
-      <c r="AB58" t="inlineStr"/>
-      <c r="AC58" t="inlineStr"/>
-      <c r="AD58" t="inlineStr"/>
-      <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -8037,6 +8064,16 @@
       <c r="AI58" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -8183,7 +8220,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -8200,6 +8236,16 @@
       <c r="AI59" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -8346,7 +8392,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -8363,6 +8408,16 @@
       <c r="AI60" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8485,6 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
           <t>United States</t>
@@ -8462,16 +8516,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr"/>
-      <c r="AB61" t="inlineStr"/>
-      <c r="AC61" t="inlineStr"/>
-      <c r="AD61" t="inlineStr"/>
-      <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -8488,6 +8532,16 @@
       <c r="AI61" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8584,6 @@
           <t>https://www.facebook.com/LazyDogFresno/</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>https://www.instagram.com/fresnobullyrescue/</t>
@@ -8587,16 +8640,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
-      <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
-      <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -8613,6 +8656,16 @@
       <c r="AI62" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -8665,7 +8718,6 @@
           <t>https://www.instagram.com/invisiblefence/</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>Raleigh</t>
@@ -8676,7 +8728,6 @@
           <t>NE</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>United States</t>
@@ -8708,16 +8759,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
-      <c r="AB63" t="inlineStr"/>
-      <c r="AC63" t="inlineStr"/>
-      <c r="AD63" t="inlineStr"/>
-      <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -8734,6 +8775,16 @@
       <c r="AI63" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -8880,7 +8931,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -8897,6 +8947,16 @@
       <c r="AI64" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -9066,6 +9126,16 @@
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
         </is>
       </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9116,10 +9186,6 @@
           <t>https://www.instagram.com/karmakennelpnw/</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -9151,15 +9217,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr"/>
-      <c r="AB66" t="inlineStr"/>
-      <c r="AC66" t="inlineStr"/>
-      <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="inlineStr">
         <is>
           <t>https://www.amazon.com/shop/karmakennelpnw?ref_=cm_sw_r_cp_ud_aipsfshop_aipsfkarmakennelpnw_7QC3Z5P9XBX354MEM7AQ</t>
@@ -9181,6 +9238,16 @@
       <c r="AI66" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -9233,10 +9300,6 @@
           <t>https://www.instagram.com/squarespace/</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
           <t>California</t>
@@ -9268,15 +9331,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr"/>
-      <c r="AB67" t="inlineStr"/>
-      <c r="AC67" t="inlineStr"/>
-      <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="inlineStr">
         <is>
           <t>https://www.amazon.com/dp/B0DQ2H855G?tag=lorettaduncan-20&amp;linkCode=osi&amp;th=1&amp;psc=1</t>
@@ -9298,6 +9352,16 @@
       <c r="AI67" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9404,6 @@
           <t>https://www.facebook.com/103462028835334/</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>https://www.instagram.com/mountain_valley_k9_kennel/</t>
@@ -9361,7 +9424,6 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
           <t>California</t>
@@ -9393,16 +9455,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="inlineStr"/>
-      <c r="AA68" t="inlineStr"/>
-      <c r="AB68" t="inlineStr"/>
-      <c r="AC68" t="inlineStr"/>
-      <c r="AD68" t="inlineStr"/>
-      <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -9419,6 +9471,16 @@
       <c r="AI68" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9533,6 @@
           <t>https://www.instagram.com/Goldenlibertydoodles/</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
           <t>El Cajon</t>
@@ -9482,7 +9543,6 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
           <t>San Diego</t>
@@ -9514,16 +9574,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
-      <c r="AA69" t="inlineStr"/>
-      <c r="AB69" t="inlineStr"/>
-      <c r="AC69" t="inlineStr"/>
-      <c r="AD69" t="inlineStr"/>
-      <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -9540,6 +9590,16 @@
       <c r="AI69" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9652,6 @@
           <t>https://www.instagram.com/oregon_bordoodles/</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>Tillamook</t>
@@ -9639,16 +9698,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="inlineStr"/>
-      <c r="AA70" t="inlineStr"/>
-      <c r="AB70" t="inlineStr"/>
-      <c r="AC70" t="inlineStr"/>
-      <c r="AD70" t="inlineStr"/>
-      <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -9665,6 +9714,16 @@
       <c r="AI70" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -9717,10 +9776,6 @@
           <t>https://www.instagram.com/coosriver_goldens/</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
           <t>Oregon</t>
@@ -9752,16 +9807,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
-      <c r="AA71" t="inlineStr"/>
-      <c r="AB71" t="inlineStr"/>
-      <c r="AC71" t="inlineStr"/>
-      <c r="AD71" t="inlineStr"/>
-      <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -9778,6 +9823,16 @@
       <c r="AI71" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -9830,10 +9885,6 @@
           <t>https://www.instagram.com/homewardboundintheheartland/</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
           <t>United States</t>
@@ -9865,15 +9916,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
-      <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="inlineStr"/>
-      <c r="AA72" t="inlineStr"/>
-      <c r="AB72" t="inlineStr"/>
-      <c r="AC72" t="inlineStr"/>
-      <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr">
         <is>
           <t>https://www.amazon.com/hz/wishlist/ls/3HO54CFOVT4TS</t>
@@ -9895,6 +9937,16 @@
       <c r="AI72" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -9947,7 +9999,6 @@
           <t>https://www.instagram.com/greenvalleypupsandpaws/</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
           <t>Ready for a puppy? Call or text 360-349-9327 | gre</t>
@@ -9994,16 +10045,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
-      <c r="Y73" t="inlineStr"/>
-      <c r="Z73" t="inlineStr"/>
-      <c r="AA73" t="inlineStr"/>
-      <c r="AB73" t="inlineStr"/>
-      <c r="AC73" t="inlineStr"/>
-      <c r="AD73" t="inlineStr"/>
-      <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -10020,6 +10061,16 @@
       <c r="AI73" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10113,6 @@
           <t>https://www.facebook.com/GoldenMeadowsRetrievers/</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>https://www.instagram.com/golden_meadows_kennels/</t>
@@ -10162,7 +10212,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -10179,6 +10228,16 @@
       <c r="AI74" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -10221,7 +10280,6 @@
           <t>https://www.facebook.com/profile.php?id=61555621016345</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>https://www.instagram.com/cutest_puppies_for_sale/</t>
@@ -10278,16 +10336,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr"/>
-      <c r="Z75" t="inlineStr"/>
-      <c r="AA75" t="inlineStr"/>
-      <c r="AB75" t="inlineStr"/>
-      <c r="AC75" t="inlineStr"/>
-      <c r="AD75" t="inlineStr"/>
-      <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -10304,6 +10352,16 @@
       <c r="AI75" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -10356,7 +10414,6 @@
           <t>https://www.instagram.com/lkbernedoodles/</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
           <t>Eugene</t>
@@ -10364,10 +10421,9 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>OR</t>
+        </is>
+      </c>
       <c r="O76" t="inlineStr">
         <is>
           <t>United States</t>
@@ -10399,15 +10455,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="inlineStr"/>
-      <c r="AA76" t="inlineStr"/>
-      <c r="AB76" t="inlineStr"/>
-      <c r="AC76" t="inlineStr"/>
-      <c r="AD76" t="inlineStr"/>
       <c r="AE76" t="inlineStr">
         <is>
           <t>https://amzn.to/3rHQNPr</t>
@@ -10429,6 +10476,16 @@
       <c r="AI76" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -10575,7 +10632,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -10592,6 +10648,16 @@
       <c r="AI77" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10700,6 @@
           <t>https://www.facebook.com/aahomaha/</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>https://www.instagram.com/americananimalhospitalomaha/</t>
@@ -10734,7 +10799,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -10751,6 +10815,16 @@
       <c r="AI78" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -10854,16 +10928,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="inlineStr"/>
-      <c r="Z79" t="inlineStr"/>
-      <c r="AA79" t="inlineStr"/>
-      <c r="AB79" t="inlineStr"/>
-      <c r="AC79" t="inlineStr"/>
-      <c r="AD79" t="inlineStr"/>
-      <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -10880,6 +10944,16 @@
       <c r="AI79" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -10922,13 +10996,11 @@
           <t>https://www.facebook.com/dominoschnoodles/</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>https://www.instagram.com/ashleedomino/</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
           <t>Moreno Valley</t>
@@ -10939,7 +11011,6 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
           <t>United States</t>
@@ -10971,16 +11042,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr"/>
-      <c r="AA80" t="inlineStr"/>
-      <c r="AB80" t="inlineStr"/>
-      <c r="AC80" t="inlineStr"/>
-      <c r="AD80" t="inlineStr"/>
-      <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -10997,6 +11058,16 @@
       <c r="AI80" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -11049,10 +11120,6 @@
           <t>https://www.instagram.com/nprlabradors/</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
           <t>United States</t>
@@ -11084,16 +11151,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
-      <c r="Y81" t="inlineStr"/>
-      <c r="Z81" t="inlineStr"/>
-      <c r="AA81" t="inlineStr"/>
-      <c r="AB81" t="inlineStr"/>
-      <c r="AC81" t="inlineStr"/>
-      <c r="AD81" t="inlineStr"/>
-      <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -11110,6 +11167,16 @@
       <c r="AI81" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -11162,10 +11229,6 @@
           <t>https://www.instagram.com/Frenchbulldogssandiego/</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
           <t>San Diego</t>
@@ -11197,16 +11260,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
-      <c r="Z82" t="inlineStr"/>
-      <c r="AA82" t="inlineStr"/>
-      <c r="AB82" t="inlineStr"/>
-      <c r="AC82" t="inlineStr"/>
-      <c r="AD82" t="inlineStr"/>
-      <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -11223,6 +11276,16 @@
       <c r="AI82" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -11326,16 +11389,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
-      <c r="Z83" t="inlineStr"/>
-      <c r="AA83" t="inlineStr"/>
-      <c r="AB83" t="inlineStr"/>
-      <c r="AC83" t="inlineStr"/>
-      <c r="AD83" t="inlineStr"/>
-      <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -11352,6 +11405,16 @@
       <c r="AI83" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -11404,7 +11467,6 @@
           <t>https://www.instagram.com/autumnharvestdoodranch/</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
           <t>Azalea</t>
@@ -11451,15 +11513,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
-      <c r="Z84" t="inlineStr"/>
-      <c r="AA84" t="inlineStr"/>
-      <c r="AB84" t="inlineStr"/>
-      <c r="AC84" t="inlineStr"/>
-      <c r="AD84" t="inlineStr"/>
       <c r="AE84" t="inlineStr">
         <is>
           <t>https://www.amazon.com/Playpen-Outdoor-Portable-Folding-Exercise/dp/B08HZ3SJF4/ref=sr_1_14?crid=1BC77UFRHXXF1&amp;keywords=xpens&amp;qid=1657768895&amp;sprefix=xpen%2Caps%2C175&amp;sr=8-14</t>
@@ -11481,6 +11534,16 @@
       <c r="AI84" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -11584,16 +11647,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
-      <c r="Y85" t="inlineStr"/>
-      <c r="Z85" t="inlineStr"/>
-      <c r="AA85" t="inlineStr"/>
-      <c r="AB85" t="inlineStr"/>
-      <c r="AC85" t="inlineStr"/>
-      <c r="AD85" t="inlineStr"/>
-      <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -11610,6 +11663,16 @@
       <c r="AI85" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11725,6 @@
           <t>https://www.instagram.com/kerryslabradoodles/</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>Lynnwood</t>
@@ -11709,16 +11771,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
-      <c r="Y86" t="inlineStr"/>
-      <c r="Z86" t="inlineStr"/>
-      <c r="AA86" t="inlineStr"/>
-      <c r="AB86" t="inlineStr"/>
-      <c r="AC86" t="inlineStr"/>
-      <c r="AD86" t="inlineStr"/>
-      <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -11735,6 +11787,16 @@
       <c r="AI86" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -11787,14 +11849,11 @@
           <t>https://www.instagram.com/sooregonknockoutbullies/</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
+          <t>OR</t>
+        </is>
+      </c>
       <c r="O87" t="inlineStr">
         <is>
           <t>Oregon</t>
@@ -11826,15 +11885,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr"/>
-      <c r="Z87" t="inlineStr"/>
-      <c r="AA87" t="inlineStr"/>
-      <c r="AB87" t="inlineStr"/>
-      <c r="AC87" t="inlineStr"/>
-      <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="inlineStr">
         <is>
           <t>https://www.amazon.com/shop/sooregonknockoutbullies?ref_=cm_sw_r_cp_ud_aipsfshop_aipsfsooregonknockoutbullies_57Y750DV14XKE4JV4HW8</t>
@@ -11856,6 +11906,16 @@
       <c r="AI87" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -11908,10 +11968,6 @@
           <t>https://www.instagram.com/nycdoggies/</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
           <t>New York</t>
@@ -11943,16 +11999,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="inlineStr"/>
-      <c r="Z88" t="inlineStr"/>
-      <c r="AA88" t="inlineStr"/>
-      <c r="AB88" t="inlineStr"/>
-      <c r="AC88" t="inlineStr"/>
-      <c r="AD88" t="inlineStr"/>
-      <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -11969,6 +12015,16 @@
       <c r="AI88" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -12021,10 +12077,6 @@
           <t>https://www.instagram.com/warottweilers/</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -12056,16 +12108,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
-      <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="inlineStr"/>
-      <c r="AA89" t="inlineStr"/>
-      <c r="AB89" t="inlineStr"/>
-      <c r="AC89" t="inlineStr"/>
-      <c r="AD89" t="inlineStr"/>
-      <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -12082,6 +12124,16 @@
       <c r="AI89" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -12228,7 +12280,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -12245,6 +12296,16 @@
       <c r="AI90" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -12297,7 +12358,6 @@
           <t>https://www.instagram.com/pdxbernedoodles/</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
           <t>Portland</t>
@@ -12308,7 +12368,6 @@
           <t>OR</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
           <t>United States</t>
@@ -12383,7 +12442,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE91" t="inlineStr"/>
       <c r="AF91" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -12400,6 +12458,16 @@
       <c r="AI91" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -12442,7 +12510,6 @@
           <t>https://www.facebook.com/shadalane/</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>https://www.instagram.com/shadalanedogs/</t>
@@ -12542,7 +12609,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE92" t="inlineStr"/>
       <c r="AF92" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -12559,6 +12625,16 @@
       <c r="AI92" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -12662,16 +12738,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr"/>
-      <c r="Y93" t="inlineStr"/>
-      <c r="Z93" t="inlineStr"/>
-      <c r="AA93" t="inlineStr"/>
-      <c r="AB93" t="inlineStr"/>
-      <c r="AC93" t="inlineStr"/>
-      <c r="AD93" t="inlineStr"/>
-      <c r="AE93" t="inlineStr"/>
       <c r="AF93" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -12688,6 +12754,16 @@
       <c r="AI93" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -12740,7 +12816,6 @@
           <t>https://www.instagram.com/mitalijainphotography/</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>Seattle</t>
@@ -12851,6 +12926,16 @@
       <c r="AI94" t="inlineStr">
         <is>
           <t>Gọi điện thoại trực tiếp hỏi: 'Do you provide a puppy take-home package?' + Gửi báo giá sỉ V2 Standard Kit</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -12903,10 +12988,6 @@
           <t>https://www.instagram.com/toyhousefrenchies/</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
           <t>United States</t>
@@ -12938,16 +13019,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
-      <c r="Y95" t="inlineStr"/>
-      <c r="Z95" t="inlineStr"/>
-      <c r="AA95" t="inlineStr"/>
-      <c r="AB95" t="inlineStr"/>
-      <c r="AC95" t="inlineStr"/>
-      <c r="AD95" t="inlineStr"/>
-      <c r="AE95" t="inlineStr"/>
       <c r="AF95" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -12964,6 +13035,16 @@
       <c r="AI95" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -13006,7 +13087,6 @@
           <t>https://www.facebook.com/Ikadoodles/</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>https://www.instagram.com/ikasdoodles/</t>
@@ -13024,7 +13104,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>init</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -13063,16 +13143,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr"/>
-      <c r="Y96" t="inlineStr"/>
-      <c r="Z96" t="inlineStr"/>
-      <c r="AA96" t="inlineStr"/>
-      <c r="AB96" t="inlineStr"/>
-      <c r="AC96" t="inlineStr"/>
-      <c r="AD96" t="inlineStr"/>
-      <c r="AE96" t="inlineStr"/>
       <c r="AF96" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -13089,6 +13159,16 @@
       <c r="AI96" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -13141,10 +13221,6 @@
           <t>https://www.instagram.com/kcsaussies/</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
           <t>United States</t>
@@ -13176,16 +13252,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
-      <c r="X97" t="inlineStr"/>
-      <c r="Y97" t="inlineStr"/>
-      <c r="Z97" t="inlineStr"/>
-      <c r="AA97" t="inlineStr"/>
-      <c r="AB97" t="inlineStr"/>
-      <c r="AC97" t="inlineStr"/>
-      <c r="AD97" t="inlineStr"/>
-      <c r="AE97" t="inlineStr"/>
       <c r="AF97" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -13202,6 +13268,16 @@
       <c r="AI97" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13325,6 @@
           <t>100064000000000</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>East 9th Street - at 2nd Avenue</t>
@@ -13344,7 +13419,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE98" t="inlineStr"/>
       <c r="AF98" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -13361,6 +13435,16 @@
       <c r="AI98" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -13425,7 +13509,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>menu false  link</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -13464,16 +13548,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
-      <c r="Y99" t="inlineStr"/>
-      <c r="Z99" t="inlineStr"/>
-      <c r="AA99" t="inlineStr"/>
-      <c r="AB99" t="inlineStr"/>
-      <c r="AC99" t="inlineStr"/>
-      <c r="AD99" t="inlineStr"/>
-      <c r="AE99" t="inlineStr"/>
       <c r="AF99" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -13490,6 +13564,16 @@
       <c r="AI99" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -13593,16 +13677,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr"/>
-      <c r="Y100" t="inlineStr"/>
-      <c r="Z100" t="inlineStr"/>
-      <c r="AA100" t="inlineStr"/>
-      <c r="AB100" t="inlineStr"/>
-      <c r="AC100" t="inlineStr"/>
-      <c r="AD100" t="inlineStr"/>
-      <c r="AE100" t="inlineStr"/>
       <c r="AF100" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -13619,6 +13693,16 @@
       <c r="AI100" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -13671,10 +13755,6 @@
           <t>https://www.instagram.com/ravenwynfarms/</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
           <t>Oregon</t>
@@ -13706,16 +13786,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V101" t="inlineStr"/>
-      <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr"/>
-      <c r="Y101" t="inlineStr"/>
-      <c r="Z101" t="inlineStr"/>
-      <c r="AA101" t="inlineStr"/>
-      <c r="AB101" t="inlineStr"/>
-      <c r="AC101" t="inlineStr"/>
-      <c r="AD101" t="inlineStr"/>
-      <c r="AE101" t="inlineStr"/>
       <c r="AF101" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -13732,6 +13802,16 @@
       <c r="AI101" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -13835,16 +13915,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V102" t="inlineStr"/>
-      <c r="W102" t="inlineStr"/>
-      <c r="X102" t="inlineStr"/>
-      <c r="Y102" t="inlineStr"/>
-      <c r="Z102" t="inlineStr"/>
-      <c r="AA102" t="inlineStr"/>
-      <c r="AB102" t="inlineStr"/>
-      <c r="AC102" t="inlineStr"/>
-      <c r="AD102" t="inlineStr"/>
-      <c r="AE102" t="inlineStr"/>
       <c r="AF102" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -13861,6 +13931,16 @@
       <c r="AI102" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -13913,10 +13993,6 @@
           <t>https://www.instagram.com/centraloregonsportingdog/</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
           <t>Oregon</t>
@@ -13948,16 +14024,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V103" t="inlineStr"/>
-      <c r="W103" t="inlineStr"/>
-      <c r="X103" t="inlineStr"/>
-      <c r="Y103" t="inlineStr"/>
-      <c r="Z103" t="inlineStr"/>
-      <c r="AA103" t="inlineStr"/>
-      <c r="AB103" t="inlineStr"/>
-      <c r="AC103" t="inlineStr"/>
-      <c r="AD103" t="inlineStr"/>
-      <c r="AE103" t="inlineStr"/>
       <c r="AF103" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -13974,6 +14040,16 @@
       <c r="AI103" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -14077,16 +14153,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V104" t="inlineStr"/>
-      <c r="W104" t="inlineStr"/>
-      <c r="X104" t="inlineStr"/>
-      <c r="Y104" t="inlineStr"/>
-      <c r="Z104" t="inlineStr"/>
-      <c r="AA104" t="inlineStr"/>
-      <c r="AB104" t="inlineStr"/>
-      <c r="AC104" t="inlineStr"/>
-      <c r="AD104" t="inlineStr"/>
-      <c r="AE104" t="inlineStr"/>
       <c r="AF104" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -14103,6 +14169,16 @@
       <c r="AI104" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14246,6 @@
           <t>ND</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
           <t>North Dakota</t>
@@ -14202,16 +14277,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V105" t="inlineStr"/>
-      <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr"/>
-      <c r="Y105" t="inlineStr"/>
-      <c r="Z105" t="inlineStr"/>
-      <c r="AA105" t="inlineStr"/>
-      <c r="AB105" t="inlineStr"/>
-      <c r="AC105" t="inlineStr"/>
-      <c r="AD105" t="inlineStr"/>
-      <c r="AE105" t="inlineStr"/>
       <c r="AF105" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -14228,6 +14293,16 @@
       <c r="AI105" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -14280,10 +14355,6 @@
           <t>https://www.instagram.com/eiswaldklm/</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
           <t>North Dakota</t>
@@ -14315,16 +14386,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr"/>
-      <c r="Y106" t="inlineStr"/>
-      <c r="Z106" t="inlineStr"/>
-      <c r="AA106" t="inlineStr"/>
-      <c r="AB106" t="inlineStr"/>
-      <c r="AC106" t="inlineStr"/>
-      <c r="AD106" t="inlineStr"/>
-      <c r="AE106" t="inlineStr"/>
       <c r="AF106" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -14341,6 +14402,16 @@
       <c r="AI106" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14479,6 @@
           <t>NE</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
           <t>Nebraska</t>
@@ -14440,16 +14510,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V107" t="inlineStr"/>
-      <c r="W107" t="inlineStr"/>
-      <c r="X107" t="inlineStr"/>
-      <c r="Y107" t="inlineStr"/>
-      <c r="Z107" t="inlineStr"/>
-      <c r="AA107" t="inlineStr"/>
-      <c r="AB107" t="inlineStr"/>
-      <c r="AC107" t="inlineStr"/>
-      <c r="AD107" t="inlineStr"/>
-      <c r="AE107" t="inlineStr"/>
       <c r="AF107" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -14466,6 +14526,16 @@
       <c r="AI107" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -14518,10 +14588,6 @@
           <t>https://www.instagram.com/abbottfamilyfarm/</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
           <t>Oregon</t>
@@ -14553,16 +14619,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V108" t="inlineStr"/>
-      <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr"/>
-      <c r="Y108" t="inlineStr"/>
-      <c r="Z108" t="inlineStr"/>
-      <c r="AA108" t="inlineStr"/>
-      <c r="AB108" t="inlineStr"/>
-      <c r="AC108" t="inlineStr"/>
-      <c r="AD108" t="inlineStr"/>
-      <c r="AE108" t="inlineStr"/>
       <c r="AF108" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -14579,6 +14635,16 @@
       <c r="AI108" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -14631,7 +14697,6 @@
           <t>https://www.instagram.com/prairiefaunakennels/</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
           <t>Turtle Lake</t>
@@ -14642,7 +14707,6 @@
           <t>ND</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
           <t>North Dakota</t>
@@ -14674,16 +14738,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V109" t="inlineStr"/>
-      <c r="W109" t="inlineStr"/>
-      <c r="X109" t="inlineStr"/>
-      <c r="Y109" t="inlineStr"/>
-      <c r="Z109" t="inlineStr"/>
-      <c r="AA109" t="inlineStr"/>
-      <c r="AB109" t="inlineStr"/>
-      <c r="AC109" t="inlineStr"/>
-      <c r="AD109" t="inlineStr"/>
-      <c r="AE109" t="inlineStr"/>
       <c r="AF109" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -14700,6 +14754,16 @@
       <c r="AI109" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -14752,10 +14816,6 @@
           <t>https://www.instagram.com/elitefrenchies_chicago/</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
           <t>Chicago</t>
@@ -14787,16 +14847,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V110" t="inlineStr"/>
-      <c r="W110" t="inlineStr"/>
-      <c r="X110" t="inlineStr"/>
-      <c r="Y110" t="inlineStr"/>
-      <c r="Z110" t="inlineStr"/>
-      <c r="AA110" t="inlineStr"/>
-      <c r="AB110" t="inlineStr"/>
-      <c r="AC110" t="inlineStr"/>
-      <c r="AD110" t="inlineStr"/>
-      <c r="AE110" t="inlineStr"/>
       <c r="AF110" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -14813,6 +14863,16 @@
       <c r="AI110" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -14959,7 +15019,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Cuộn 25% trang)</t>
         </is>
       </c>
-      <c r="AE111" t="inlineStr"/>
       <c r="AF111" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -14976,6 +15035,16 @@
       <c r="AI111" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -15040,7 +15109,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -15079,16 +15148,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V112" t="inlineStr"/>
-      <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr"/>
-      <c r="Y112" t="inlineStr"/>
-      <c r="Z112" t="inlineStr"/>
-      <c r="AA112" t="inlineStr"/>
-      <c r="AB112" t="inlineStr"/>
-      <c r="AC112" t="inlineStr"/>
-      <c r="AD112" t="inlineStr"/>
-      <c r="AE112" t="inlineStr"/>
       <c r="AF112" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -15105,6 +15164,16 @@
       <c r="AI112" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -15208,16 +15277,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V113" t="inlineStr"/>
-      <c r="W113" t="inlineStr"/>
-      <c r="X113" t="inlineStr"/>
-      <c r="Y113" t="inlineStr"/>
-      <c r="Z113" t="inlineStr"/>
-      <c r="AA113" t="inlineStr"/>
-      <c r="AB113" t="inlineStr"/>
-      <c r="AC113" t="inlineStr"/>
-      <c r="AD113" t="inlineStr"/>
-      <c r="AE113" t="inlineStr"/>
       <c r="AF113" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -15234,6 +15293,16 @@
       <c r="AI113" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -15276,20 +15345,16 @@
           <t>https://www.facebook.com/roostervalleylabradors/</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>https://www.instagram.com/roostervalleylab/</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
+          <t>CA</t>
+        </is>
+      </c>
       <c r="O114" t="inlineStr">
         <is>
           <t>California</t>
@@ -15321,16 +15386,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V114" t="inlineStr"/>
-      <c r="W114" t="inlineStr"/>
-      <c r="X114" t="inlineStr"/>
-      <c r="Y114" t="inlineStr"/>
-      <c r="Z114" t="inlineStr"/>
-      <c r="AA114" t="inlineStr"/>
-      <c r="AB114" t="inlineStr"/>
-      <c r="AC114" t="inlineStr"/>
-      <c r="AD114" t="inlineStr"/>
-      <c r="AE114" t="inlineStr"/>
       <c r="AF114" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -15347,6 +15402,16 @@
       <c r="AI114" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -15389,7 +15454,6 @@
           <t>https://www.facebook.com/BedNBiscuitRanch/</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>https://www.instagram.com/bednbiscuitranch/</t>
@@ -15489,7 +15553,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE115" t="inlineStr"/>
       <c r="AF115" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -15506,6 +15569,16 @@
       <c r="AI115" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -15609,16 +15682,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V116" t="inlineStr"/>
-      <c r="W116" t="inlineStr"/>
-      <c r="X116" t="inlineStr"/>
-      <c r="Y116" t="inlineStr"/>
-      <c r="Z116" t="inlineStr"/>
-      <c r="AA116" t="inlineStr"/>
-      <c r="AB116" t="inlineStr"/>
-      <c r="AC116" t="inlineStr"/>
-      <c r="AD116" t="inlineStr"/>
-      <c r="AE116" t="inlineStr"/>
       <c r="AF116" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -15635,6 +15698,16 @@
       <c r="AI116" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -15687,7 +15760,6 @@
           <t>https://www.instagram.com/2ndchancedogrescue/</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
           <t>San Diego</t>
@@ -15698,7 +15770,6 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
           <t>United States</t>
@@ -15773,7 +15844,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE117" t="inlineStr"/>
       <c r="AF117" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -15790,6 +15860,16 @@
       <c r="AI117" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -15893,16 +15973,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V118" t="inlineStr"/>
-      <c r="W118" t="inlineStr"/>
-      <c r="X118" t="inlineStr"/>
-      <c r="Y118" t="inlineStr"/>
-      <c r="Z118" t="inlineStr"/>
-      <c r="AA118" t="inlineStr"/>
-      <c r="AB118" t="inlineStr"/>
-      <c r="AC118" t="inlineStr"/>
-      <c r="AD118" t="inlineStr"/>
-      <c r="AE118" t="inlineStr"/>
       <c r="AF118" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -15919,6 +15989,16 @@
       <c r="AI118" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -16022,16 +16102,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V119" t="inlineStr"/>
-      <c r="W119" t="inlineStr"/>
-      <c r="X119" t="inlineStr"/>
-      <c r="Y119" t="inlineStr"/>
-      <c r="Z119" t="inlineStr"/>
-      <c r="AA119" t="inlineStr"/>
-      <c r="AB119" t="inlineStr"/>
-      <c r="AC119" t="inlineStr"/>
-      <c r="AD119" t="inlineStr"/>
-      <c r="AE119" t="inlineStr"/>
       <c r="AF119" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -16048,6 +16118,16 @@
       <c r="AI119" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -16194,7 +16274,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE120" t="inlineStr"/>
       <c r="AF120" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -16211,6 +16290,16 @@
       <c r="AI120" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -16357,7 +16446,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE121" t="inlineStr"/>
       <c r="AF121" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -16374,6 +16462,16 @@
       <c r="AI121" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -16426,10 +16524,6 @@
           <t>https://www.instagram.com/MONT_BLANC_DOBERMANS/</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
           <t>United States</t>
@@ -16461,16 +16555,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr"/>
-      <c r="X122" t="inlineStr"/>
-      <c r="Y122" t="inlineStr"/>
-      <c r="Z122" t="inlineStr"/>
-      <c r="AA122" t="inlineStr"/>
-      <c r="AB122" t="inlineStr"/>
-      <c r="AC122" t="inlineStr"/>
-      <c r="AD122" t="inlineStr"/>
-      <c r="AE122" t="inlineStr"/>
       <c r="AF122" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -16487,6 +16571,16 @@
       <c r="AI122" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -16590,16 +16684,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V123" t="inlineStr"/>
-      <c r="W123" t="inlineStr"/>
-      <c r="X123" t="inlineStr"/>
-      <c r="Y123" t="inlineStr"/>
-      <c r="Z123" t="inlineStr"/>
-      <c r="AA123" t="inlineStr"/>
-      <c r="AB123" t="inlineStr"/>
-      <c r="AC123" t="inlineStr"/>
-      <c r="AD123" t="inlineStr"/>
-      <c r="AE123" t="inlineStr"/>
       <c r="AF123" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -16616,6 +16700,16 @@
       <c r="AI123" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -16762,7 +16856,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE124" t="inlineStr"/>
       <c r="AF124" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -16779,6 +16872,16 @@
       <c r="AI124" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -16882,16 +16985,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V125" t="inlineStr"/>
-      <c r="W125" t="inlineStr"/>
-      <c r="X125" t="inlineStr"/>
-      <c r="Y125" t="inlineStr"/>
-      <c r="Z125" t="inlineStr"/>
-      <c r="AA125" t="inlineStr"/>
-      <c r="AB125" t="inlineStr"/>
-      <c r="AC125" t="inlineStr"/>
-      <c r="AD125" t="inlineStr"/>
-      <c r="AE125" t="inlineStr"/>
       <c r="AF125" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -16908,6 +17001,16 @@
       <c r="AI125" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -16960,10 +17063,6 @@
           <t>https://www.instagram.com/howlistic/</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
           <t>United States</t>
@@ -16995,16 +17094,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V126" t="inlineStr"/>
-      <c r="W126" t="inlineStr"/>
-      <c r="X126" t="inlineStr"/>
-      <c r="Y126" t="inlineStr"/>
-      <c r="Z126" t="inlineStr"/>
-      <c r="AA126" t="inlineStr"/>
-      <c r="AB126" t="inlineStr"/>
-      <c r="AC126" t="inlineStr"/>
-      <c r="AD126" t="inlineStr"/>
-      <c r="AE126" t="inlineStr"/>
       <c r="AF126" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -17021,6 +17110,16 @@
       <c r="AI126" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -17167,7 +17266,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE127" t="inlineStr"/>
       <c r="AF127" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -17184,6 +17282,16 @@
       <c r="AI127" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -17330,7 +17438,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE128" t="inlineStr"/>
       <c r="AF128" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -17347,6 +17454,16 @@
       <c r="AI128" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -17399,7 +17516,6 @@
           <t>https://www.instagram.com/gooddog/</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
           <t>Washington</t>
@@ -17410,7 +17526,6 @@
           <t>DC</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
           <t>United States</t>
@@ -17442,16 +17557,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V129" t="inlineStr"/>
-      <c r="W129" t="inlineStr"/>
-      <c r="X129" t="inlineStr"/>
-      <c r="Y129" t="inlineStr"/>
-      <c r="Z129" t="inlineStr"/>
-      <c r="AA129" t="inlineStr"/>
-      <c r="AB129" t="inlineStr"/>
-      <c r="AC129" t="inlineStr"/>
-      <c r="AD129" t="inlineStr"/>
-      <c r="AE129" t="inlineStr"/>
       <c r="AF129" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -17468,6 +17573,16 @@
       <c r="AI129" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -17505,8 +17620,6 @@
           <t>https://www.campbowwow.com/rochester/</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>https://www.instagram.com/campbowwowrochester/</t>
@@ -17606,7 +17719,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE130" t="inlineStr"/>
       <c r="AF130" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -17623,6 +17735,16 @@
       <c r="AI130" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -17660,8 +17782,6 @@
           <t>https://seattlecanineclub.com/sodo/</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>https://www.instagram.com/seattlecanineclub/</t>
@@ -17761,7 +17881,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE131" t="inlineStr"/>
       <c r="AF131" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -17778,6 +17897,16 @@
       <c r="AI131" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -17820,8 +17949,6 @@
           <t>https://www.facebook.com/The-Pet-Clinic-126603360748490/</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>2509 S. 140th Circle</t>
@@ -17916,7 +18043,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE132" t="inlineStr"/>
       <c r="AF132" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -17933,6 +18059,16 @@
       <c r="AI132" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -17975,7 +18111,6 @@
           <t>https://www.facebook.com/deercreekdoodles/</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>https://www.instagram.com/deercreek.doodles/</t>
@@ -18032,15 +18167,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V133" t="inlineStr"/>
-      <c r="W133" t="inlineStr"/>
-      <c r="X133" t="inlineStr"/>
-      <c r="Y133" t="inlineStr"/>
-      <c r="Z133" t="inlineStr"/>
-      <c r="AA133" t="inlineStr"/>
-      <c r="AB133" t="inlineStr"/>
-      <c r="AC133" t="inlineStr"/>
-      <c r="AD133" t="inlineStr"/>
       <c r="AE133" t="inlineStr">
         <is>
           <t>https://amzn.to/3cHilvM</t>
@@ -18062,6 +18188,16 @@
       <c r="AI133" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -18099,8 +18235,6 @@
           <t>https://www.doggoneproblems.com/</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>https://www.instagram.com/doggoneproblems/</t>
@@ -18200,7 +18334,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE134" t="inlineStr"/>
       <c r="AF134" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -18217,6 +18350,16 @@
       <c r="AI134" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -18254,8 +18397,6 @@
           <t>https://seattlecanineclub.com/south-lake-union/</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>https://www.instagram.com/seattlecanineclub/</t>
@@ -18355,7 +18496,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE135" t="inlineStr"/>
       <c r="AF135" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -18372,6 +18512,16 @@
       <c r="AI135" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -18399,7 +18549,6 @@
           <t>aps@alohapet.services</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
           <t>https://alohapet.services/</t>
@@ -18420,7 +18569,6 @@
           <t>https://www.instagram.com/aloha_pet_services/</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
           <t>Carpio</t>
@@ -18467,16 +18615,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V136" t="inlineStr"/>
-      <c r="W136" t="inlineStr"/>
-      <c r="X136" t="inlineStr"/>
-      <c r="Y136" t="inlineStr"/>
-      <c r="Z136" t="inlineStr"/>
-      <c r="AA136" t="inlineStr"/>
-      <c r="AB136" t="inlineStr"/>
-      <c r="AC136" t="inlineStr"/>
-      <c r="AD136" t="inlineStr"/>
-      <c r="AE136" t="inlineStr"/>
       <c r="AF136" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -18493,6 +18631,16 @@
       <c r="AI136" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -18639,7 +18787,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE137" t="inlineStr"/>
       <c r="AF137" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -18656,6 +18803,16 @@
       <c r="AI137" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -18683,7 +18840,6 @@
           <t>info@muddypawsrescue.org</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
           <t>https://www.muddypawsrescue.org/</t>
@@ -18704,10 +18860,6 @@
           <t>https://www.instagram.com/muddypawsrescuenyc/</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
           <t>New York</t>
@@ -18739,16 +18891,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V138" t="inlineStr"/>
-      <c r="W138" t="inlineStr"/>
-      <c r="X138" t="inlineStr"/>
-      <c r="Y138" t="inlineStr"/>
-      <c r="Z138" t="inlineStr"/>
-      <c r="AA138" t="inlineStr"/>
-      <c r="AB138" t="inlineStr"/>
-      <c r="AC138" t="inlineStr"/>
-      <c r="AD138" t="inlineStr"/>
-      <c r="AE138" t="inlineStr"/>
       <c r="AF138" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -18765,6 +18907,16 @@
       <c r="AI138" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -18792,7 +18944,6 @@
           <t>info@dogeducated.com</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
           <t>https://dogeducated.com/</t>
@@ -18928,6 +19079,16 @@
       <c r="AI139" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19235,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE140" t="inlineStr"/>
       <c r="AF140" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -19091,6 +19251,16 @@
       <c r="AI140" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -19133,13 +19303,11 @@
           <t>https://www.facebook.com/californiashihtzus/</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>https://www.instagram.com/sensational_shih_tzus/</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
           <t>Manteca</t>
@@ -19186,16 +19354,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V141" t="inlineStr"/>
-      <c r="W141" t="inlineStr"/>
-      <c r="X141" t="inlineStr"/>
-      <c r="Y141" t="inlineStr"/>
-      <c r="Z141" t="inlineStr"/>
-      <c r="AA141" t="inlineStr"/>
-      <c r="AB141" t="inlineStr"/>
-      <c r="AC141" t="inlineStr"/>
-      <c r="AD141" t="inlineStr"/>
-      <c r="AE141" t="inlineStr"/>
       <c r="AF141" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -19212,6 +19370,16 @@
       <c r="AI141" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -19249,8 +19417,6 @@
           <t>https://wagsandruffs.com/</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>https://www.instagram.com/wagsandruffs/</t>
@@ -19350,7 +19516,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE142" t="inlineStr"/>
       <c r="AF142" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -19367,6 +19532,16 @@
       <c r="AI142" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -19419,10 +19594,6 @@
           <t>https://www.instagram.com/vip_chihuahua/</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr">
         <is>
           <t>Portland</t>
@@ -19454,16 +19625,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V143" t="inlineStr"/>
-      <c r="W143" t="inlineStr"/>
-      <c r="X143" t="inlineStr"/>
-      <c r="Y143" t="inlineStr"/>
-      <c r="Z143" t="inlineStr"/>
-      <c r="AA143" t="inlineStr"/>
-      <c r="AB143" t="inlineStr"/>
-      <c r="AC143" t="inlineStr"/>
-      <c r="AD143" t="inlineStr"/>
-      <c r="AE143" t="inlineStr"/>
       <c r="AF143" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -19480,6 +19641,16 @@
       <c r="AI143" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -19507,7 +19678,6 @@
           <t>suncrestlabradoodles@gmail.com</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
           <t>https://www.suncrestlabradoodles.com/</t>
@@ -19643,6 +19813,16 @@
       <c r="AI144" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -19685,13 +19865,11 @@
           <t>https://www.facebook.com/Oregonoodles/</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>https://www.instagram.com/oregondoodlesnpoodles/</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
           <t>Eugene</t>
@@ -19702,7 +19880,6 @@
           <t>OR</t>
         </is>
       </c>
-      <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr">
         <is>
           <t>Oregon</t>
@@ -19734,16 +19911,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V145" t="inlineStr"/>
-      <c r="W145" t="inlineStr"/>
-      <c r="X145" t="inlineStr"/>
-      <c r="Y145" t="inlineStr"/>
-      <c r="Z145" t="inlineStr"/>
-      <c r="AA145" t="inlineStr"/>
-      <c r="AB145" t="inlineStr"/>
-      <c r="AC145" t="inlineStr"/>
-      <c r="AD145" t="inlineStr"/>
-      <c r="AE145" t="inlineStr"/>
       <c r="AF145" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -19760,6 +19927,16 @@
       <c r="AI145" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -19802,16 +19979,11 @@
           <t>https://www.facebook.com/Lakeshoredoodles/</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>https://www.instagram.com/lakeshoredoodles/</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr">
         <is>
           <t>Fairport United States</t>
@@ -19843,16 +20015,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V146" t="inlineStr"/>
-      <c r="W146" t="inlineStr"/>
-      <c r="X146" t="inlineStr"/>
-      <c r="Y146" t="inlineStr"/>
-      <c r="Z146" t="inlineStr"/>
-      <c r="AA146" t="inlineStr"/>
-      <c r="AB146" t="inlineStr"/>
-      <c r="AC146" t="inlineStr"/>
-      <c r="AD146" t="inlineStr"/>
-      <c r="AE146" t="inlineStr"/>
       <c r="AF146" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -19869,6 +20031,16 @@
       <c r="AI146" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -19911,13 +20083,11 @@
           <t>https://www.facebook.com/PUPPYGUYZ/</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>https://www.instagram.com/puppyguysinc/</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
           <t>Westbury</t>
@@ -19925,7 +20095,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -19964,16 +20134,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V147" t="inlineStr"/>
-      <c r="W147" t="inlineStr"/>
-      <c r="X147" t="inlineStr"/>
-      <c r="Y147" t="inlineStr"/>
-      <c r="Z147" t="inlineStr"/>
-      <c r="AA147" t="inlineStr"/>
-      <c r="AB147" t="inlineStr"/>
-      <c r="AC147" t="inlineStr"/>
-      <c r="AD147" t="inlineStr"/>
-      <c r="AE147" t="inlineStr"/>
       <c r="AF147" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -19990,6 +20150,16 @@
       <c r="AI147" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -20032,20 +20202,16 @@
           <t>https://www.facebook.com/vonhaanenkennels/</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>https://www.instagram.com/vonhaanendoberman/</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
+          <t>CA</t>
+        </is>
+      </c>
       <c r="O148" t="inlineStr">
         <is>
           <t>California</t>
@@ -20077,16 +20243,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V148" t="inlineStr"/>
-      <c r="W148" t="inlineStr"/>
-      <c r="X148" t="inlineStr"/>
-      <c r="Y148" t="inlineStr"/>
-      <c r="Z148" t="inlineStr"/>
-      <c r="AA148" t="inlineStr"/>
-      <c r="AB148" t="inlineStr"/>
-      <c r="AC148" t="inlineStr"/>
-      <c r="AD148" t="inlineStr"/>
-      <c r="AE148" t="inlineStr"/>
       <c r="AF148" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -20103,6 +20259,16 @@
       <c r="AI148" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -20145,13 +20311,11 @@
           <t>https://www.facebook.com/crimsoncrownbeagles/</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>https://www.instagram.com/ccbeagles/</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
           <t>Regent</t>
@@ -20198,16 +20362,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V149" t="inlineStr"/>
-      <c r="W149" t="inlineStr"/>
-      <c r="X149" t="inlineStr"/>
-      <c r="Y149" t="inlineStr"/>
-      <c r="Z149" t="inlineStr"/>
-      <c r="AA149" t="inlineStr"/>
-      <c r="AB149" t="inlineStr"/>
-      <c r="AC149" t="inlineStr"/>
-      <c r="AD149" t="inlineStr"/>
-      <c r="AE149" t="inlineStr"/>
       <c r="AF149" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -20224,6 +20378,16 @@
       <c r="AI149" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -20261,8 +20425,6 @@
           <t>https://westseattlewonderdogs.com/</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>https://www.instagram.com/west.seattle.wonderdogs/</t>
@@ -20362,7 +20524,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE150" t="inlineStr"/>
       <c r="AF150" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -20379,6 +20540,16 @@
       <c r="AI150" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -20421,8 +20592,6 @@
           <t>https://www.facebook.com/Providencepups/</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
           <t>30224 227th St</t>
@@ -20438,7 +20607,6 @@
           <t>IA</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr">
         <is>
           <t>Des Moines</t>
@@ -20470,16 +20638,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V151" t="inlineStr"/>
-      <c r="W151" t="inlineStr"/>
-      <c r="X151" t="inlineStr"/>
-      <c r="Y151" t="inlineStr"/>
-      <c r="Z151" t="inlineStr"/>
-      <c r="AA151" t="inlineStr"/>
-      <c r="AB151" t="inlineStr"/>
-      <c r="AC151" t="inlineStr"/>
-      <c r="AD151" t="inlineStr"/>
-      <c r="AE151" t="inlineStr"/>
       <c r="AF151" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -20496,6 +20654,16 @@
       <c r="AI151" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -20538,7 +20706,6 @@
           <t>https://www.facebook.com/RoyalEmpirepoodles/</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>https://www.instagram.com/royalempirepnw/</t>
@@ -20595,16 +20762,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V152" t="inlineStr"/>
-      <c r="W152" t="inlineStr"/>
-      <c r="X152" t="inlineStr"/>
-      <c r="Y152" t="inlineStr"/>
-      <c r="Z152" t="inlineStr"/>
-      <c r="AA152" t="inlineStr"/>
-      <c r="AB152" t="inlineStr"/>
-      <c r="AC152" t="inlineStr"/>
-      <c r="AD152" t="inlineStr"/>
-      <c r="AE152" t="inlineStr"/>
       <c r="AF152" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -20621,6 +20778,16 @@
       <c r="AI152" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -20668,7 +20835,6 @@
           <t>100064000000000</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
           <t>40746 144th St</t>
@@ -20720,16 +20886,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V153" t="inlineStr"/>
-      <c r="W153" t="inlineStr"/>
-      <c r="X153" t="inlineStr"/>
-      <c r="Y153" t="inlineStr"/>
-      <c r="Z153" t="inlineStr"/>
-      <c r="AA153" t="inlineStr"/>
-      <c r="AB153" t="inlineStr"/>
-      <c r="AC153" t="inlineStr"/>
-      <c r="AD153" t="inlineStr"/>
-      <c r="AE153" t="inlineStr"/>
       <c r="AF153" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -20746,6 +20902,16 @@
       <c r="AI153" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -20788,16 +20954,11 @@
           <t>https://www.facebook.com/cascadeberners/</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>https://www.instagram.com/cascadeberners/</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr">
         <is>
           <t>Oregon</t>
@@ -20829,16 +20990,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V154" t="inlineStr"/>
-      <c r="W154" t="inlineStr"/>
-      <c r="X154" t="inlineStr"/>
-      <c r="Y154" t="inlineStr"/>
-      <c r="Z154" t="inlineStr"/>
-      <c r="AA154" t="inlineStr"/>
-      <c r="AB154" t="inlineStr"/>
-      <c r="AC154" t="inlineStr"/>
-      <c r="AD154" t="inlineStr"/>
-      <c r="AE154" t="inlineStr"/>
       <c r="AF154" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -20855,6 +21006,16 @@
       <c r="AI154" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -20897,7 +21058,6 @@
           <t>https://www.facebook.com/californiadulcedoodles/</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
           <t>https://www.instagram.com/californiadulcedoodles/</t>
@@ -20918,7 +21078,6 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr">
         <is>
           <t>California</t>
@@ -20950,15 +21109,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V155" t="inlineStr"/>
-      <c r="W155" t="inlineStr"/>
-      <c r="X155" t="inlineStr"/>
-      <c r="Y155" t="inlineStr"/>
-      <c r="Z155" t="inlineStr"/>
-      <c r="AA155" t="inlineStr"/>
-      <c r="AB155" t="inlineStr"/>
-      <c r="AC155" t="inlineStr"/>
-      <c r="AD155" t="inlineStr"/>
       <c r="AE155" t="inlineStr">
         <is>
           <t>https://amzn.to/4aT7dtD</t>
@@ -20980,6 +21130,16 @@
       <c r="AI155" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -21032,7 +21192,6 @@
           <t>https://www.instagram.com/animalhaven/</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
           <t>New York</t>
@@ -21040,7 +21199,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -21143,6 +21302,16 @@
       <c r="AI156" t="inlineStr">
         <is>
           <t>Gọi điện thoại trực tiếp hỏi: 'Do you provide a puppy take-home package?' + Gửi báo giá sỉ V2 Standard Kit</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -21185,16 +21354,11 @@
           <t>https://www.facebook.com/Sierra-Springs-Australian-Labradoodles-194814241052484/; https://www.facebook.com/SSDoodles/</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>https://www.instagram.com/sierraspringsdoodles/</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr">
         <is>
           <t>California</t>
@@ -21226,15 +21390,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V157" t="inlineStr"/>
-      <c r="W157" t="inlineStr"/>
-      <c r="X157" t="inlineStr"/>
-      <c r="Y157" t="inlineStr"/>
-      <c r="Z157" t="inlineStr"/>
-      <c r="AA157" t="inlineStr"/>
-      <c r="AB157" t="inlineStr"/>
-      <c r="AC157" t="inlineStr"/>
-      <c r="AD157" t="inlineStr"/>
       <c r="AE157" t="inlineStr">
         <is>
           <t>https://amzn.to/3CfjZmy</t>
@@ -21256,6 +21411,16 @@
       <c r="AI157" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -21303,7 +21468,6 @@
           <t>61569600000000</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
           <t>maltese puppies oregon, maltese puppies for sale in oregon, maltese breeders portland oregon, maltese breeders oregon</t>
@@ -21355,16 +21519,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V158" t="inlineStr"/>
-      <c r="W158" t="inlineStr"/>
-      <c r="X158" t="inlineStr"/>
-      <c r="Y158" t="inlineStr"/>
-      <c r="Z158" t="inlineStr"/>
-      <c r="AA158" t="inlineStr"/>
-      <c r="AB158" t="inlineStr"/>
-      <c r="AC158" t="inlineStr"/>
-      <c r="AD158" t="inlineStr"/>
-      <c r="AE158" t="inlineStr"/>
       <c r="AF158" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -21381,6 +21535,16 @@
       <c r="AI158" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -21423,7 +21587,6 @@
           <t>https://www.facebook.com/summitcaninetraining/</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>https://www.instagram.com/summitk9training/</t>
@@ -21441,7 +21604,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -21480,16 +21643,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V159" t="inlineStr"/>
-      <c r="W159" t="inlineStr"/>
-      <c r="X159" t="inlineStr"/>
-      <c r="Y159" t="inlineStr"/>
-      <c r="Z159" t="inlineStr"/>
-      <c r="AA159" t="inlineStr"/>
-      <c r="AB159" t="inlineStr"/>
-      <c r="AC159" t="inlineStr"/>
-      <c r="AD159" t="inlineStr"/>
-      <c r="AE159" t="inlineStr"/>
       <c r="AF159" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -21506,6 +21659,16 @@
       <c r="AI159" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -21652,7 +21815,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE160" t="inlineStr"/>
       <c r="AF160" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -21669,6 +21831,16 @@
       <c r="AI160" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -21815,7 +21987,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE161" t="inlineStr"/>
       <c r="AF161" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -21832,6 +22003,16 @@
       <c r="AI161" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -21884,7 +22065,6 @@
           <t>https://www.instagram.com/dogwatchfence/</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
           <t>Bismarck</t>
@@ -21895,7 +22075,6 @@
           <t>ND</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr">
         <is>
           <t>United States</t>
@@ -21970,7 +22149,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE162" t="inlineStr"/>
       <c r="AF162" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -21987,6 +22165,16 @@
       <c r="AI162" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -22029,7 +22217,6 @@
           <t>https://www.facebook.com/katieskennelomaha/</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
           <t>https://www.instagram.com/katieskennel/</t>
@@ -22129,7 +22316,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE163" t="inlineStr"/>
       <c r="AF163" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -22146,6 +22332,16 @@
       <c r="AI163" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -22188,7 +22384,6 @@
           <t>https://www.facebook.com/Wonder-Puppy-63054291299/</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
           <t>https://www.instagram.com/wonderpuppypdx/</t>
@@ -22288,7 +22483,6 @@
           <t>Chưa click SP cụ thể (Chỉ lướt trang Products - Dòng Pet · Chưa cuộn (ở đầu trang))</t>
         </is>
       </c>
-      <c r="AE164" t="inlineStr"/>
       <c r="AF164" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -22305,6 +22499,16 @@
       <c r="AI164" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -22369,7 +22573,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -22408,16 +22612,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V165" t="inlineStr"/>
-      <c r="W165" t="inlineStr"/>
-      <c r="X165" t="inlineStr"/>
-      <c r="Y165" t="inlineStr"/>
-      <c r="Z165" t="inlineStr"/>
-      <c r="AA165" t="inlineStr"/>
-      <c r="AB165" t="inlineStr"/>
-      <c r="AC165" t="inlineStr"/>
-      <c r="AD165" t="inlineStr"/>
-      <c r="AE165" t="inlineStr"/>
       <c r="AF165" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -22434,6 +22628,16 @@
       <c r="AI165" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -22537,16 +22741,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V166" t="inlineStr"/>
-      <c r="W166" t="inlineStr"/>
-      <c r="X166" t="inlineStr"/>
-      <c r="Y166" t="inlineStr"/>
-      <c r="Z166" t="inlineStr"/>
-      <c r="AA166" t="inlineStr"/>
-      <c r="AB166" t="inlineStr"/>
-      <c r="AC166" t="inlineStr"/>
-      <c r="AD166" t="inlineStr"/>
-      <c r="AE166" t="inlineStr"/>
       <c r="AF166" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -22563,6 +22757,16 @@
       <c r="AI166" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -22605,12 +22809,6 @@
           <t>https://www.facebook.com/HSEOPR/</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr">
         <is>
           <t>Oregon</t>
@@ -22642,16 +22840,6 @@
           <t>Thành công</t>
         </is>
       </c>
-      <c r="V167" t="inlineStr"/>
-      <c r="W167" t="inlineStr"/>
-      <c r="X167" t="inlineStr"/>
-      <c r="Y167" t="inlineStr"/>
-      <c r="Z167" t="inlineStr"/>
-      <c r="AA167" t="inlineStr"/>
-      <c r="AB167" t="inlineStr"/>
-      <c r="AC167" t="inlineStr"/>
-      <c r="AD167" t="inlineStr"/>
-      <c r="AE167" t="inlineStr"/>
       <c r="AF167" t="inlineStr">
         <is>
           <t>Amazon link not found</t>
@@ -22668,6 +22856,16 @@
       <c r="AI167" t="inlineStr">
         <is>
           <t>Nhắn tin tương tác qua Fanpage Facebook/Instagram</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -22766,16 +22964,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr"/>
-      <c r="V168" t="inlineStr"/>
-      <c r="W168" t="inlineStr"/>
-      <c r="X168" t="inlineStr"/>
-      <c r="Y168" t="inlineStr"/>
-      <c r="Z168" t="inlineStr"/>
-      <c r="AA168" t="inlineStr"/>
-      <c r="AB168" t="inlineStr"/>
-      <c r="AC168" t="inlineStr"/>
-      <c r="AD168" t="inlineStr"/>
       <c r="AE168" t="inlineStr">
         <is>
           <t>https://www.amazon.com/Amazon-Basics-Foldable-Metal-Single/dp/B09G4Y2C7D/ref=sr_1_1_sspa?c=ts&amp;keywords=Dog+Crates&amp;qid=1675646661&amp;s=pet-supplies&amp;sr=1-1-spons&amp;ts_id=2975401011&amp;psc=1&amp;spLa=ZW5jcnlwdGVkUXVhbGlmaWVyPUEyS1hOUURPSUVQMlBWJmVuY3J5cHRlZElkPUEwNjA0NjE4MjRESUZWRE1JSjFFNCZlbmNyeXB0ZWRBZElkPUExMDQ2OTI3MkhGRVc4NE5VNFlIViZ3aWRnZXROYW1lPXNwX2F0ZiZhY3Rpb249Y2xpY2tSZWRpcmVjdCZkb05vdExvZ0NsaWNrPXRydWU=</t>
@@ -22797,6 +22985,16 @@
       <c r="AI168" t="inlineStr">
         <is>
           <t>Gửi chuỗi email marketing tự động giới thiệu Take-Home Kit + Follow-up telesale</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>United States</t>
         </is>
       </c>
     </row>
